--- a/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_d_otrasrel_a_2021_atacama.xlsx
+++ b/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_d_otrasrel_a_2021_atacama.xlsx
@@ -141,7 +141,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-18 14:23</t>
+    <t xml:space="preserve">2026-09-24 01:13</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -582,7 +582,7 @@
         <v>-0.16</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>-0.38</v>
+        <v>-0.39</v>
       </c>
     </row>
     <row r="3">
@@ -628,7 +628,7 @@
         <v>-0.2</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>-0.23</v>
+        <v>-0.24</v>
       </c>
     </row>
     <row r="5">
@@ -648,10 +648,10 @@
         <v>0.04</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>0.05</v>
+        <v>0.04</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>-0.01</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -694,7 +694,7 @@
         <v>-0.45</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>0.09</v>
+        <v>0.1</v>
       </c>
       <c r="G7" s="2" t="n">
         <v>-0.55</v>
@@ -766,7 +766,7 @@
         <v>0.16</v>
       </c>
       <c r="G10" s="2" t="n">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
     </row>
     <row r="11">
@@ -855,10 +855,10 @@
         <v>-0.43</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>-0.02</v>
+        <v>0.15</v>
       </c>
       <c r="G14" s="2" t="n">
-        <v>-0.41</v>
+        <v>-0.58</v>
       </c>
     </row>
     <row r="15">
@@ -878,10 +878,10 @@
         <v>-0.28</v>
       </c>
       <c r="F15" s="2" t="n">
-        <v>0.03</v>
+        <v>0.14</v>
       </c>
       <c r="G15" s="2" t="n">
-        <v>-0.3</v>
+        <v>-0.42</v>
       </c>
     </row>
     <row r="16">
@@ -901,10 +901,10 @@
         <v>-0.66</v>
       </c>
       <c r="F16" s="2" t="n">
-        <v>-0.28</v>
+        <v>-0.19</v>
       </c>
       <c r="G16" s="2" t="n">
-        <v>-0.39</v>
+        <v>-0.47</v>
       </c>
     </row>
     <row r="17">
@@ -924,10 +924,10 @@
         <v>-0.56</v>
       </c>
       <c r="F17" s="2" t="n">
-        <v>-0.17</v>
+        <v>-0.26</v>
       </c>
       <c r="G17" s="2" t="n">
-        <v>-0.39</v>
+        <v>-0.3</v>
       </c>
     </row>
     <row r="18">
@@ -973,7 +973,7 @@
         <v>-0.23</v>
       </c>
       <c r="G19" s="2" t="n">
-        <v>-0.34</v>
+        <v>-0.35</v>
       </c>
     </row>
     <row r="20">
@@ -996,7 +996,7 @@
         <v>-0.35</v>
       </c>
       <c r="G20" s="2" t="n">
-        <v>-0.19</v>
+        <v>-0.2</v>
       </c>
     </row>
     <row r="21">
@@ -1016,10 +1016,10 @@
         <v>0.35</v>
       </c>
       <c r="F21" s="2" t="n">
-        <v>-0.09</v>
+        <v>0.13</v>
       </c>
       <c r="G21" s="2" t="n">
-        <v>0.44</v>
+        <v>0.21</v>
       </c>
     </row>
     <row r="22">
@@ -1039,10 +1039,10 @@
         <v>0.56</v>
       </c>
       <c r="F22" s="2" t="n">
-        <v>-0.05</v>
+        <v>-0.17</v>
       </c>
       <c r="G22" s="2" t="n">
-        <v>0.61</v>
+        <v>0.73</v>
       </c>
     </row>
     <row r="23">
@@ -1226,7 +1226,7 @@
         <v>-0.09</v>
       </c>
       <c r="G30" s="2" t="n">
-        <v>-0.32</v>
+        <v>-0.31</v>
       </c>
     </row>
     <row r="31">
@@ -1246,7 +1246,7 @@
         <v>-0.36</v>
       </c>
       <c r="F31" s="2" t="n">
-        <v>-0.07</v>
+        <v>-0.08</v>
       </c>
       <c r="G31" s="2" t="n">
         <v>-0.28</v>
@@ -1361,10 +1361,10 @@
         <v>0.64</v>
       </c>
       <c r="F36" s="2" t="n">
-        <v>0.2</v>
+        <v>0.22</v>
       </c>
       <c r="G36" s="2" t="n">
-        <v>0.44</v>
+        <v>0.42</v>
       </c>
     </row>
     <row r="37">
@@ -1384,10 +1384,10 @@
         <v>-0.18</v>
       </c>
       <c r="F37" s="2" t="n">
-        <v>-0.1</v>
+        <v>0</v>
       </c>
       <c r="G37" s="2" t="n">
-        <v>-0.09</v>
+        <v>-0.19</v>
       </c>
     </row>
     <row r="38">
@@ -1407,10 +1407,10 @@
         <v>-0.33</v>
       </c>
       <c r="F38" s="2" t="n">
-        <v>-0.01</v>
+        <v>0.03</v>
       </c>
       <c r="G38" s="2" t="n">
-        <v>-0.32</v>
+        <v>-0.36</v>
       </c>
     </row>
     <row r="39">
@@ -1433,7 +1433,7 @@
         <v>-0.22</v>
       </c>
       <c r="G39" s="2" t="n">
-        <v>-0.11</v>
+        <v>-0.1</v>
       </c>
     </row>
     <row r="40">
@@ -1522,10 +1522,10 @@
         <v>0.48</v>
       </c>
       <c r="F43" s="2" t="n">
-        <v>0.03</v>
+        <v>0.13</v>
       </c>
       <c r="G43" s="2" t="n">
-        <v>0.45</v>
+        <v>0.36</v>
       </c>
     </row>
     <row r="44">
@@ -1545,10 +1545,10 @@
         <v>-0.15</v>
       </c>
       <c r="F44" s="2" t="n">
-        <v>-0.19</v>
+        <v>-0.22</v>
       </c>
       <c r="G44" s="2" t="n">
-        <v>0.04</v>
+        <v>0.07</v>
       </c>
     </row>
     <row r="45">
@@ -2028,10 +2028,10 @@
         <v>-0.4</v>
       </c>
       <c r="F65" s="2" t="n">
-        <v>0.07</v>
+        <v>-0.12</v>
       </c>
       <c r="G65" s="2" t="n">
-        <v>-0.47</v>
+        <v>-0.28</v>
       </c>
     </row>
     <row r="66">
@@ -2051,10 +2051,10 @@
         <v>0.26</v>
       </c>
       <c r="F66" s="2" t="n">
-        <v>0.33</v>
+        <v>0.35</v>
       </c>
       <c r="G66" s="2" t="n">
-        <v>-0.07</v>
+        <v>-0.09</v>
       </c>
     </row>
     <row r="67">

--- a/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_d_otrasrel_a_2021_atacama.xlsx
+++ b/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_d_otrasrel_a_2021_atacama.xlsx
@@ -120,7 +120,7 @@
     <t xml:space="preserve">Migración</t>
   </si>
   <si>
-    <t xml:space="preserve">Movilidad interna (CMI)</t>
+    <t xml:space="preserve">Movilidad interna comunal (CMI)</t>
   </si>
   <si>
     <t xml:space="preserve">Saldo migratorio</t>
@@ -141,7 +141,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-24 01:13</t>
+    <t xml:space="preserve">2026-10-01 23:08</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_d_otrasrel_a_2021_atacama.xlsx
+++ b/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_d_otrasrel_a_2021_atacama.xlsx
@@ -141,7 +141,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-01 23:08</t>
+    <t xml:space="preserve">2026-10-05 19:46</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
